--- a/Relatórios Modelo/Santos/consulta_xlsx_0.xlsx
+++ b/Relatórios Modelo/Santos/consulta_xlsx_0.xlsx
@@ -1,13 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://homehealthcaredr-my.sharepoint.com/personal/jackson_junior_homedoctor_com_br/Documents/Documentos/Antigravity/Conferência do Faturamento/Relatórios Modelo/Santos/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_CCAA257D342FFC91801DBC12D8E11AB4739E89DA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ext" r:id="rId3" sheetId="1"/>
+    <sheet name="ext" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -476,15 +497,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -494,7 +515,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -511,2372 +532,2563 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU18"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.53125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="14.3359375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.42578125" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="5.7109375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="5.7109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="6.421875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="24.65234375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.4140625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="19.26171875" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="21.94921875" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="21.64453125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="17.375" customWidth="true" bestFit="true"/>
-    <col min="13" max="13" width="21.8125" customWidth="true" bestFit="true"/>
-    <col min="14" max="14" width="107.20703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="17.375" customWidth="true" bestFit="true"/>
-    <col min="16" max="16" width="21.8125" customWidth="true" bestFit="true"/>
-    <col min="17" max="17" width="55.1484375" customWidth="true" bestFit="true"/>
-    <col min="18" max="18" width="89.03125" customWidth="true" bestFit="true"/>
-    <col min="19" max="19" width="6.2734375" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.16015625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="10.98828125" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="85.87109375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="194.88671875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="19.42578125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="26.80859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="28.72265625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="20.125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="18.2578125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="10.4609375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="12.23046875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.23046875" customWidth="true" bestFit="true"/>
-    <col min="32" max="32" width="12.23046875" customWidth="true" bestFit="true"/>
-    <col min="33" max="33" width="10.44140625" customWidth="true" bestFit="true"/>
-    <col min="34" max="34" width="11.1015625" customWidth="true" bestFit="true"/>
-    <col min="35" max="35" width="20.82421875" customWidth="true" bestFit="true"/>
-    <col min="36" max="36" width="33.0625" customWidth="true" bestFit="true"/>
-    <col min="37" max="37" width="18.8984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="13.2890625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="25.51953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="30.125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="27.1328125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="15.4296875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.01953125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="31.3671875" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="13.8984375" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="11.54296875" customWidth="true" bestFit="true"/>
-    <col min="47" max="47" width="26.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="107.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="89" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="85.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="194.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="33" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="43" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="0">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>23</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>24</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>25</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>27</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" t="s" s="0">
+      <c r="AH1" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" t="s" s="0">
+      <c r="AI1" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" t="s" s="0">
+      <c r="AJ1" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" t="s" s="0">
+      <c r="AK1" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" t="s" s="0">
+      <c r="AL1" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" t="s" s="0">
+      <c r="AM1" t="s">
         <v>35</v>
       </c>
-      <c r="AN1" t="s" s="0">
+      <c r="AN1" t="s">
         <v>36</v>
       </c>
-      <c r="AO1" t="s" s="0">
+      <c r="AO1" t="s">
         <v>37</v>
       </c>
-      <c r="AP1" t="s" s="0">
+      <c r="AP1" t="s">
         <v>38</v>
       </c>
-      <c r="AQ1" t="s" s="0">
+      <c r="AQ1" t="s">
         <v>39</v>
       </c>
-      <c r="AR1" t="s" s="0">
+      <c r="AR1" t="s">
         <v>40</v>
       </c>
-      <c r="AS1" t="s" s="0">
+      <c r="AS1" t="s">
         <v>41</v>
       </c>
-      <c r="AT1" t="s" s="0">
+      <c r="AT1" t="s">
         <v>42</v>
       </c>
-      <c r="AU1" t="s" s="0">
+      <c r="AU1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
+    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>46</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>2864.0</v>
-      </c>
-      <c r="E2" t="n" s="0">
-        <v>2868.0</v>
-      </c>
-      <c r="F2" t="s" s="0">
+      <c r="D2">
+        <v>2864</v>
+      </c>
+      <c r="E2">
+        <v>2868</v>
+      </c>
+      <c r="F2" t="s">
         <v>47</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="0"/>
-      <c r="I2" s="0"/>
-      <c r="J2" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L2" t="s" s="0">
+      <c r="J2" t="s">
+        <v>49</v>
+      </c>
+      <c r="K2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" t="s">
         <v>50</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>51</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>52</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>53</v>
       </c>
-      <c r="P2" s="0"/>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>54</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>55</v>
       </c>
-      <c r="S2" s="0"/>
-      <c r="T2" t="s" s="0">
+      <c r="T2" t="s">
         <v>56</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>57</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>58</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>59</v>
       </c>
-      <c r="X2" t="n" s="1">
+      <c r="X2" s="1">
         <v>86197.41</v>
       </c>
-      <c r="Y2" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z2" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA2" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB2" t="n" s="1">
+      <c r="Y2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="1">
         <v>86197.41</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>60</v>
       </c>
-      <c r="AD2" t="n" s="1">
+      <c r="AD2" s="1">
         <v>1723.95</v>
       </c>
-      <c r="AE2" t="n" s="1">
+      <c r="AE2" s="1">
         <v>84.47</v>
       </c>
-      <c r="AF2" t="n" s="1">
+      <c r="AF2" s="1">
         <v>760.26</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>61</v>
       </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AH2" t="s">
         <v>62</v>
       </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AI2" t="s">
         <v>63</v>
       </c>
-      <c r="AJ2" t="s" s="0">
+      <c r="AJ2" t="s">
         <v>64</v>
       </c>
-      <c r="AK2" t="s" s="0">
+      <c r="AK2" t="s">
         <v>62</v>
       </c>
-      <c r="AL2" s="0"/>
-      <c r="AM2" s="0"/>
-      <c r="AN2" s="0"/>
-      <c r="AO2" s="0"/>
-      <c r="AP2" t="s" s="0">
+      <c r="AP2" t="s">
         <v>65</v>
       </c>
-      <c r="AQ2" s="0"/>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>66</v>
       </c>
-      <c r="AS2" t="s" s="0">
+      <c r="AS2" t="s">
         <v>67</v>
       </c>
-      <c r="AT2" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU2" t="s" s="0">
+      <c r="AT2">
+        <v>100586516</v>
+      </c>
+      <c r="AU2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
+    <row r="3" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>45</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>68</v>
       </c>
-      <c r="D3" t="n" s="0">
-        <v>2865.0</v>
-      </c>
-      <c r="E3" t="n" s="0">
-        <v>2869.0</v>
-      </c>
-      <c r="F3" t="s" s="0">
+      <c r="D3">
+        <v>2865</v>
+      </c>
+      <c r="E3">
+        <v>2869</v>
+      </c>
+      <c r="F3" t="s">
         <v>47</v>
       </c>
-      <c r="G3" t="s" s="0">
+      <c r="G3" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="0"/>
-      <c r="I3" s="0"/>
-      <c r="J3" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K3" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L3" t="s" s="0">
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" t="s">
         <v>50</v>
       </c>
-      <c r="M3" t="s" s="0">
+      <c r="M3" t="s">
         <v>51</v>
       </c>
-      <c r="N3" t="s" s="0">
+      <c r="N3" t="s">
         <v>52</v>
       </c>
-      <c r="O3" t="s" s="0">
+      <c r="O3" t="s">
         <v>70</v>
       </c>
-      <c r="P3" s="0"/>
-      <c r="Q3" t="s" s="0">
+      <c r="Q3" t="s">
         <v>71</v>
       </c>
-      <c r="R3" t="s" s="0">
+      <c r="R3" t="s">
         <v>72</v>
       </c>
-      <c r="S3" s="0"/>
-      <c r="T3" t="s" s="0">
+      <c r="T3" t="s">
         <v>56</v>
       </c>
-      <c r="U3" t="s" s="0">
+      <c r="U3" t="s">
         <v>57</v>
       </c>
-      <c r="V3" t="s" s="0">
+      <c r="V3" t="s">
         <v>58</v>
       </c>
-      <c r="W3" t="s" s="0">
+      <c r="W3" t="s">
         <v>73</v>
       </c>
-      <c r="X3" t="n" s="1">
-        <v>2056.0</v>
-      </c>
-      <c r="Y3" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z3" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA3" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB3" t="n" s="1">
-        <v>2056.0</v>
-      </c>
-      <c r="AC3" t="s" s="0">
+      <c r="X3" s="1">
+        <v>2056</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>2056</v>
+      </c>
+      <c r="AC3" t="s">
         <v>60</v>
       </c>
-      <c r="AD3" t="n" s="1">
+      <c r="AD3" s="1">
         <v>41.12</v>
       </c>
-      <c r="AE3" t="n" s="1">
-        <v>2.01</v>
-      </c>
-      <c r="AF3" t="n" s="1">
+      <c r="AE3" s="1">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AF3" s="1">
         <v>18.13</v>
       </c>
-      <c r="AG3" t="s" s="0">
+      <c r="AG3" t="s">
         <v>61</v>
       </c>
-      <c r="AH3" t="s" s="0">
+      <c r="AH3" t="s">
         <v>62</v>
       </c>
-      <c r="AI3" t="s" s="0">
+      <c r="AI3" t="s">
         <v>63</v>
       </c>
-      <c r="AJ3" t="s" s="0">
+      <c r="AJ3" t="s">
         <v>64</v>
       </c>
-      <c r="AK3" t="s" s="0">
+      <c r="AK3" t="s">
         <v>62</v>
       </c>
-      <c r="AL3" s="0"/>
-      <c r="AM3" s="0"/>
-      <c r="AN3" s="0"/>
-      <c r="AO3" s="0"/>
-      <c r="AP3" t="s" s="0">
+      <c r="AP3" t="s">
         <v>65</v>
       </c>
-      <c r="AQ3" s="0"/>
-      <c r="AR3" t="s" s="0">
+      <c r="AR3" t="s">
         <v>66</v>
       </c>
-      <c r="AS3" t="s" s="0">
+      <c r="AS3" t="s">
         <v>67</v>
       </c>
-      <c r="AT3" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU3" t="s" s="0">
+      <c r="AT3">
+        <v>100586516</v>
+      </c>
+      <c r="AU3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
+    <row r="4" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>44</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="n" s="0">
-        <v>2866.0</v>
-      </c>
-      <c r="E4" t="n" s="0">
-        <v>2870.0</v>
-      </c>
-      <c r="F4" t="s" s="0">
+      <c r="D4">
+        <v>2866</v>
+      </c>
+      <c r="E4">
+        <v>2870</v>
+      </c>
+      <c r="F4" t="s">
         <v>47</v>
       </c>
-      <c r="G4" t="s" s="0">
+      <c r="G4" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="0"/>
-      <c r="I4" s="0"/>
-      <c r="J4" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K4" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s" s="0">
+      <c r="J4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" t="s">
         <v>50</v>
       </c>
-      <c r="M4" t="s" s="0">
+      <c r="M4" t="s">
         <v>51</v>
       </c>
-      <c r="N4" t="s" s="0">
+      <c r="N4" t="s">
         <v>52</v>
       </c>
-      <c r="O4" t="s" s="0">
+      <c r="O4" t="s">
         <v>76</v>
       </c>
-      <c r="P4" s="0"/>
-      <c r="Q4" t="s" s="0">
+      <c r="Q4" t="s">
         <v>77</v>
       </c>
-      <c r="R4" t="s" s="0">
+      <c r="R4" t="s">
         <v>78</v>
       </c>
-      <c r="S4" s="0"/>
-      <c r="T4" t="s" s="0">
+      <c r="T4" t="s">
         <v>56</v>
       </c>
-      <c r="U4" t="s" s="0">
+      <c r="U4" t="s">
         <v>57</v>
       </c>
-      <c r="V4" t="s" s="0">
+      <c r="V4" t="s">
         <v>58</v>
       </c>
-      <c r="W4" t="s" s="0">
+      <c r="W4" t="s">
         <v>79</v>
       </c>
-      <c r="X4" t="n" s="1">
-        <v>856.0</v>
-      </c>
-      <c r="Y4" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z4" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA4" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB4" t="n" s="1">
-        <v>856.0</v>
-      </c>
-      <c r="AC4" t="s" s="0">
+      <c r="X4" s="1">
+        <v>856</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>856</v>
+      </c>
+      <c r="AC4" t="s">
         <v>60</v>
       </c>
-      <c r="AD4" t="n" s="1">
+      <c r="AD4" s="1">
         <v>17.12</v>
       </c>
-      <c r="AE4" t="n" s="1">
+      <c r="AE4" s="1">
         <v>0.84</v>
       </c>
-      <c r="AF4" t="n" s="1">
+      <c r="AF4" s="1">
         <v>7.55</v>
       </c>
-      <c r="AG4" t="s" s="0">
+      <c r="AG4" t="s">
         <v>61</v>
       </c>
-      <c r="AH4" t="s" s="0">
+      <c r="AH4" t="s">
         <v>62</v>
       </c>
-      <c r="AI4" t="s" s="0">
+      <c r="AI4" t="s">
         <v>63</v>
       </c>
-      <c r="AJ4" t="s" s="0">
+      <c r="AJ4" t="s">
         <v>64</v>
       </c>
-      <c r="AK4" t="s" s="0">
+      <c r="AK4" t="s">
         <v>62</v>
       </c>
-      <c r="AL4" s="0"/>
-      <c r="AM4" s="0"/>
-      <c r="AN4" s="0"/>
-      <c r="AO4" s="0"/>
-      <c r="AP4" t="s" s="0">
+      <c r="AP4" t="s">
         <v>65</v>
       </c>
-      <c r="AQ4" s="0"/>
-      <c r="AR4" t="s" s="0">
+      <c r="AR4" t="s">
         <v>66</v>
       </c>
-      <c r="AS4" t="s" s="0">
+      <c r="AS4" t="s">
         <v>67</v>
       </c>
-      <c r="AT4" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU4" t="s" s="0">
+      <c r="AT4">
+        <v>100586516</v>
+      </c>
+      <c r="AU4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
+    <row r="5" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s" s="0">
+      <c r="B5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s" s="0">
+      <c r="C5" t="s">
         <v>80</v>
       </c>
-      <c r="D5" t="n" s="0">
-        <v>2867.0</v>
-      </c>
-      <c r="E5" t="n" s="0">
-        <v>2871.0</v>
-      </c>
-      <c r="F5" t="s" s="0">
+      <c r="D5">
+        <v>2867</v>
+      </c>
+      <c r="E5">
+        <v>2871</v>
+      </c>
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="G5" t="s" s="0">
+      <c r="G5" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="0"/>
-      <c r="I5" s="0"/>
-      <c r="J5" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K5" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L5" t="s" s="0">
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" t="s">
         <v>50</v>
       </c>
-      <c r="M5" t="s" s="0">
+      <c r="M5" t="s">
         <v>51</v>
       </c>
-      <c r="N5" t="s" s="0">
+      <c r="N5" t="s">
         <v>52</v>
       </c>
-      <c r="O5" t="s" s="0">
+      <c r="O5" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="0"/>
-      <c r="Q5" t="s" s="0">
+      <c r="Q5" t="s">
         <v>71</v>
       </c>
-      <c r="R5" t="s" s="0">
+      <c r="R5" t="s">
         <v>72</v>
       </c>
-      <c r="S5" s="0"/>
-      <c r="T5" t="s" s="0">
+      <c r="T5" t="s">
         <v>56</v>
       </c>
-      <c r="U5" t="s" s="0">
+      <c r="U5" t="s">
         <v>57</v>
       </c>
-      <c r="V5" t="s" s="0">
+      <c r="V5" t="s">
         <v>58</v>
       </c>
-      <c r="W5" t="s" s="0">
+      <c r="W5" t="s">
         <v>82</v>
       </c>
-      <c r="X5" t="n" s="1">
-        <v>240.0</v>
-      </c>
-      <c r="Y5" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z5" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA5" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB5" t="n" s="1">
-        <v>240.0</v>
-      </c>
-      <c r="AC5" t="s" s="0">
+      <c r="X5" s="1">
+        <v>240</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>240</v>
+      </c>
+      <c r="AC5" t="s">
         <v>60</v>
       </c>
-      <c r="AD5" t="n" s="1">
+      <c r="AD5" s="1">
         <v>4.8</v>
       </c>
-      <c r="AE5" t="n" s="1">
+      <c r="AE5" s="1">
         <v>0.24</v>
       </c>
-      <c r="AF5" t="n" s="1">
+      <c r="AF5" s="1">
         <v>2.12</v>
       </c>
-      <c r="AG5" t="s" s="0">
+      <c r="AG5" t="s">
         <v>61</v>
       </c>
-      <c r="AH5" t="s" s="0">
+      <c r="AH5" t="s">
         <v>62</v>
       </c>
-      <c r="AI5" t="s" s="0">
+      <c r="AI5" t="s">
         <v>63</v>
       </c>
-      <c r="AJ5" t="s" s="0">
+      <c r="AJ5" t="s">
         <v>64</v>
       </c>
-      <c r="AK5" t="s" s="0">
+      <c r="AK5" t="s">
         <v>62</v>
       </c>
-      <c r="AL5" s="0"/>
-      <c r="AM5" s="0"/>
-      <c r="AN5" s="0"/>
-      <c r="AO5" s="0"/>
-      <c r="AP5" t="s" s="0">
+      <c r="AP5" t="s">
         <v>65</v>
       </c>
-      <c r="AQ5" s="0"/>
-      <c r="AR5" t="s" s="0">
+      <c r="AR5" t="s">
         <v>66</v>
       </c>
-      <c r="AS5" t="s" s="0">
+      <c r="AS5" t="s">
         <v>67</v>
       </c>
-      <c r="AT5" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU5" t="s" s="0">
+      <c r="AT5">
+        <v>100586516</v>
+      </c>
+      <c r="AU5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
+    <row r="6" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" t="s" s="0">
+      <c r="B6" t="s">
         <v>45</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>83</v>
       </c>
-      <c r="D6" t="n" s="0">
-        <v>2868.0</v>
-      </c>
-      <c r="E6" t="n" s="0">
-        <v>2872.0</v>
-      </c>
-      <c r="F6" t="s" s="0">
+      <c r="D6">
+        <v>2868</v>
+      </c>
+      <c r="E6">
+        <v>2872</v>
+      </c>
+      <c r="F6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" t="s" s="0">
+      <c r="G6" t="s">
         <v>84</v>
       </c>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
-      <c r="J6" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K6" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L6" t="s" s="0">
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s">
         <v>50</v>
       </c>
-      <c r="M6" t="s" s="0">
+      <c r="M6" t="s">
         <v>51</v>
       </c>
-      <c r="N6" t="s" s="0">
+      <c r="N6" t="s">
         <v>52</v>
       </c>
-      <c r="O6" t="s" s="0">
+      <c r="O6" t="s">
         <v>85</v>
       </c>
-      <c r="P6" s="0"/>
-      <c r="Q6" t="s" s="0">
+      <c r="Q6" t="s">
         <v>86</v>
       </c>
-      <c r="R6" t="s" s="0">
+      <c r="R6" t="s">
         <v>87</v>
       </c>
-      <c r="S6" s="0"/>
-      <c r="T6" t="s" s="0">
+      <c r="T6" t="s">
         <v>56</v>
       </c>
-      <c r="U6" t="s" s="0">
+      <c r="U6" t="s">
         <v>57</v>
       </c>
-      <c r="V6" t="s" s="0">
+      <c r="V6" t="s">
         <v>58</v>
       </c>
-      <c r="W6" t="s" s="0">
+      <c r="W6" t="s">
         <v>88</v>
       </c>
-      <c r="X6" t="n" s="1">
+      <c r="X6" s="1">
         <v>42472.55</v>
       </c>
-      <c r="Y6" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z6" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA6" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB6" t="n" s="1">
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="1">
         <v>42472.55</v>
       </c>
-      <c r="AC6" t="s" s="0">
+      <c r="AC6" t="s">
         <v>60</v>
       </c>
-      <c r="AD6" t="n" s="1">
+      <c r="AD6" s="1">
         <v>849.45</v>
       </c>
-      <c r="AE6" t="n" s="1">
+      <c r="AE6" s="1">
         <v>41.62</v>
       </c>
-      <c r="AF6" t="n" s="1">
+      <c r="AF6" s="1">
         <v>374.61</v>
       </c>
-      <c r="AG6" t="s" s="0">
+      <c r="AG6" t="s">
         <v>61</v>
       </c>
-      <c r="AH6" t="s" s="0">
+      <c r="AH6" t="s">
         <v>62</v>
       </c>
-      <c r="AI6" t="s" s="0">
+      <c r="AI6" t="s">
         <v>63</v>
       </c>
-      <c r="AJ6" t="s" s="0">
+      <c r="AJ6" t="s">
         <v>64</v>
       </c>
-      <c r="AK6" t="s" s="0">
+      <c r="AK6" t="s">
         <v>62</v>
       </c>
-      <c r="AL6" s="0"/>
-      <c r="AM6" s="0"/>
-      <c r="AN6" s="0"/>
-      <c r="AO6" s="0"/>
-      <c r="AP6" t="s" s="0">
+      <c r="AP6" t="s">
         <v>65</v>
       </c>
-      <c r="AQ6" s="0"/>
-      <c r="AR6" t="s" s="0">
+      <c r="AR6" t="s">
         <v>66</v>
       </c>
-      <c r="AS6" t="s" s="0">
+      <c r="AS6" t="s">
         <v>67</v>
       </c>
-      <c r="AT6" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU6" t="s" s="0">
+      <c r="AT6">
+        <v>100586516</v>
+      </c>
+      <c r="AU6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
+    <row r="7" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s" s="0">
+      <c r="B7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="C7" t="s">
         <v>89</v>
       </c>
-      <c r="D7" t="n" s="0">
-        <v>2869.0</v>
-      </c>
-      <c r="E7" t="n" s="0">
-        <v>2873.0</v>
-      </c>
-      <c r="F7" t="s" s="0">
+      <c r="D7">
+        <v>2869</v>
+      </c>
+      <c r="E7">
+        <v>2873</v>
+      </c>
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="G7" t="s" s="0">
+      <c r="G7" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="0"/>
-      <c r="I7" s="0"/>
-      <c r="J7" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K7" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L7" t="s" s="0">
+      <c r="J7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" t="s">
         <v>50</v>
       </c>
-      <c r="M7" t="s" s="0">
+      <c r="M7" t="s">
         <v>51</v>
       </c>
-      <c r="N7" t="s" s="0">
+      <c r="N7" t="s">
         <v>52</v>
       </c>
-      <c r="O7" t="s" s="0">
+      <c r="O7" t="s">
         <v>91</v>
       </c>
-      <c r="P7" s="0"/>
-      <c r="Q7" t="s" s="0">
+      <c r="Q7" t="s">
         <v>92</v>
       </c>
-      <c r="R7" t="s" s="0">
+      <c r="R7" t="s">
         <v>93</v>
       </c>
-      <c r="S7" s="0"/>
-      <c r="T7" t="s" s="0">
+      <c r="T7" t="s">
         <v>56</v>
       </c>
-      <c r="U7" t="s" s="0">
+      <c r="U7" t="s">
         <v>57</v>
       </c>
-      <c r="V7" t="s" s="0">
+      <c r="V7" t="s">
         <v>58</v>
       </c>
-      <c r="W7" t="s" s="0">
+      <c r="W7" t="s">
         <v>94</v>
       </c>
-      <c r="X7" t="n" s="1">
-        <v>538.32</v>
-      </c>
-      <c r="Y7" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z7" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA7" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB7" t="n" s="1">
-        <v>538.32</v>
-      </c>
-      <c r="AC7" t="s" s="0">
+      <c r="X7" s="1">
+        <v>538.32000000000005</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>538.32000000000005</v>
+      </c>
+      <c r="AC7" t="s">
         <v>60</v>
       </c>
-      <c r="AD7" t="n" s="1">
+      <c r="AD7" s="1">
         <v>10.77</v>
       </c>
-      <c r="AE7" t="n" s="1">
+      <c r="AE7" s="1">
         <v>0.53</v>
       </c>
-      <c r="AF7" t="n" s="1">
+      <c r="AF7" s="1">
         <v>4.75</v>
       </c>
-      <c r="AG7" t="s" s="0">
+      <c r="AG7" t="s">
         <v>61</v>
       </c>
-      <c r="AH7" t="s" s="0">
+      <c r="AH7" t="s">
         <v>62</v>
       </c>
-      <c r="AI7" t="s" s="0">
+      <c r="AI7" t="s">
         <v>63</v>
       </c>
-      <c r="AJ7" t="s" s="0">
+      <c r="AJ7" t="s">
         <v>64</v>
       </c>
-      <c r="AK7" t="s" s="0">
+      <c r="AK7" t="s">
         <v>62</v>
       </c>
-      <c r="AL7" s="0"/>
-      <c r="AM7" s="0"/>
-      <c r="AN7" s="0"/>
-      <c r="AO7" s="0"/>
-      <c r="AP7" t="s" s="0">
+      <c r="AP7" t="s">
         <v>65</v>
       </c>
-      <c r="AQ7" s="0"/>
-      <c r="AR7" t="s" s="0">
+      <c r="AR7" t="s">
         <v>66</v>
       </c>
-      <c r="AS7" t="s" s="0">
+      <c r="AS7" t="s">
         <v>67</v>
       </c>
-      <c r="AT7" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU7" t="s" s="0">
+      <c r="AT7">
+        <v>100586516</v>
+      </c>
+      <c r="AU7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" t="s" s="0">
+      <c r="B8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" t="s" s="0">
+      <c r="C8" t="s">
         <v>95</v>
       </c>
-      <c r="D8" t="n" s="0">
-        <v>2870.0</v>
-      </c>
-      <c r="E8" s="0"/>
-      <c r="F8" t="s" s="0">
+      <c r="D8">
+        <v>2870</v>
+      </c>
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-      <c r="G8" t="s" s="0">
+      <c r="G8" t="s">
         <v>96</v>
       </c>
-      <c r="H8" s="0"/>
-      <c r="I8" s="0"/>
-      <c r="J8" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K8" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L8" t="s" s="0">
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" t="s">
         <v>50</v>
       </c>
-      <c r="M8" t="s" s="0">
+      <c r="M8" t="s">
         <v>51</v>
       </c>
-      <c r="N8" t="s" s="0">
+      <c r="N8" t="s">
         <v>52</v>
       </c>
-      <c r="O8" t="s" s="0">
+      <c r="O8" t="s">
         <v>97</v>
       </c>
-      <c r="P8" t="s" s="0">
+      <c r="P8" t="s">
         <v>98</v>
       </c>
-      <c r="Q8" t="s" s="0">
+      <c r="Q8" t="s">
         <v>99</v>
       </c>
-      <c r="R8" t="s" s="0">
+      <c r="R8" t="s">
         <v>100</v>
       </c>
-      <c r="S8" s="0"/>
-      <c r="T8" t="s" s="0">
+      <c r="T8" t="s">
         <v>56</v>
       </c>
-      <c r="U8" t="s" s="0">
+      <c r="U8" t="s">
         <v>101</v>
       </c>
-      <c r="V8" t="s" s="0">
+      <c r="V8" t="s">
         <v>102</v>
       </c>
-      <c r="W8" t="s" s="0">
+      <c r="W8" t="s">
         <v>103</v>
       </c>
-      <c r="X8" t="n" s="1">
+      <c r="X8" s="1">
         <v>1033401.82</v>
       </c>
-      <c r="Y8" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z8" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA8" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB8" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC8" t="s" s="0">
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="s">
         <v>60</v>
       </c>
-      <c r="AD8" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE8" t="n" s="1">
+      <c r="AD8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="1">
         <v>1012.73</v>
       </c>
-      <c r="AF8" t="n" s="1">
+      <c r="AF8" s="1">
         <v>9114.6</v>
       </c>
-      <c r="AG8" t="s" s="0">
+      <c r="AG8" t="s">
         <v>104</v>
       </c>
-      <c r="AH8" t="s" s="0">
+      <c r="AH8" t="s">
         <v>105</v>
       </c>
-      <c r="AI8" t="s" s="0">
+      <c r="AI8" t="s">
         <v>63</v>
       </c>
-      <c r="AJ8" t="s" s="0">
+      <c r="AJ8" t="s">
         <v>64</v>
       </c>
-      <c r="AK8" t="s" s="0">
+      <c r="AK8" t="s">
         <v>62</v>
       </c>
-      <c r="AL8" t="s" s="0">
+      <c r="AL8" t="s">
         <v>106</v>
       </c>
-      <c r="AM8" t="n" s="0">
-        <v>30101.0</v>
-      </c>
-      <c r="AN8" t="s" s="0">
+      <c r="AM8">
+        <v>30101</v>
+      </c>
+      <c r="AN8" t="s">
         <v>107</v>
       </c>
-      <c r="AO8" t="s" s="0">
+      <c r="AO8" t="s">
         <v>108</v>
       </c>
-      <c r="AP8" t="s" s="0">
+      <c r="AP8" t="s">
         <v>65</v>
       </c>
-      <c r="AQ8" s="0"/>
-      <c r="AR8" t="s" s="0">
+      <c r="AR8" t="s">
         <v>66</v>
       </c>
-      <c r="AS8" t="s" s="0">
+      <c r="AS8" t="s">
         <v>67</v>
       </c>
-      <c r="AT8" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU8" t="s" s="0">
+      <c r="AT8">
+        <v>100586516</v>
+      </c>
+      <c r="AU8" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s" s="0">
+      <c r="B9" t="s">
         <v>45</v>
       </c>
-      <c r="C9" t="s" s="0">
+      <c r="C9" t="s">
         <v>109</v>
       </c>
-      <c r="D9" t="n" s="0">
-        <v>2871.0</v>
-      </c>
-      <c r="E9" t="n" s="0">
-        <v>2874.0</v>
-      </c>
-      <c r="F9" t="s" s="0">
+      <c r="D9">
+        <v>2871</v>
+      </c>
+      <c r="E9">
+        <v>2874</v>
+      </c>
+      <c r="F9" t="s">
         <v>47</v>
       </c>
-      <c r="G9" t="s" s="0">
+      <c r="G9" t="s">
         <v>110</v>
       </c>
-      <c r="H9" s="0"/>
-      <c r="I9" s="0"/>
-      <c r="J9" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K9" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L9" t="s" s="0">
+      <c r="J9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" t="s">
         <v>50</v>
       </c>
-      <c r="M9" t="s" s="0">
+      <c r="M9" t="s">
         <v>51</v>
       </c>
-      <c r="N9" t="s" s="0">
+      <c r="N9" t="s">
         <v>52</v>
       </c>
-      <c r="O9" t="s" s="0">
+      <c r="O9" t="s">
         <v>97</v>
       </c>
-      <c r="P9" t="s" s="0">
+      <c r="P9" t="s">
         <v>98</v>
       </c>
-      <c r="Q9" t="s" s="0">
+      <c r="Q9" t="s">
         <v>99</v>
       </c>
-      <c r="R9" t="s" s="0">
+      <c r="R9" t="s">
         <v>111</v>
       </c>
-      <c r="S9" s="0"/>
-      <c r="T9" t="s" s="0">
+      <c r="T9" t="s">
         <v>56</v>
       </c>
-      <c r="U9" t="s" s="0">
+      <c r="U9" t="s">
         <v>57</v>
       </c>
-      <c r="V9" t="s" s="0">
+      <c r="V9" t="s">
         <v>58</v>
       </c>
-      <c r="W9" t="s" s="0">
+      <c r="W9" t="s">
         <v>112</v>
       </c>
-      <c r="X9" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y9" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z9" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA9" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB9" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC9" t="s" s="0">
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="s">
         <v>60</v>
       </c>
-      <c r="AD9" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE9" t="n" s="1">
-        <v>18.74</v>
-      </c>
-      <c r="AF9" t="n" s="1">
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AF9" s="1">
         <v>168.66</v>
       </c>
-      <c r="AG9" t="s" s="0">
+      <c r="AG9" t="s">
         <v>104</v>
       </c>
-      <c r="AH9" t="s" s="0">
+      <c r="AH9" t="s">
         <v>105</v>
       </c>
-      <c r="AI9" t="s" s="0">
+      <c r="AI9" t="s">
         <v>63</v>
       </c>
-      <c r="AJ9" t="s" s="0">
+      <c r="AJ9" t="s">
         <v>64</v>
       </c>
-      <c r="AK9" t="s" s="0">
+      <c r="AK9" t="s">
         <v>62</v>
       </c>
-      <c r="AL9" s="0"/>
-      <c r="AM9" s="0"/>
-      <c r="AN9" s="0"/>
-      <c r="AO9" s="0"/>
-      <c r="AP9" t="s" s="0">
+      <c r="AP9" t="s">
         <v>113</v>
       </c>
-      <c r="AQ9" t="s" s="0">
+      <c r="AQ9" t="s">
         <v>114</v>
       </c>
-      <c r="AR9" t="s" s="0">
+      <c r="AR9" t="s">
         <v>115</v>
       </c>
-      <c r="AS9" t="s" s="0">
+      <c r="AS9" t="s">
         <v>67</v>
       </c>
-      <c r="AT9" s="0"/>
-      <c r="AU9" t="s" s="0">
+      <c r="AU9" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="s" s="0">
+    <row r="10" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>44</v>
       </c>
-      <c r="B10" t="s" s="0">
+      <c r="B10" t="s">
         <v>45</v>
       </c>
-      <c r="C10" t="s" s="0">
+      <c r="C10" t="s">
         <v>116</v>
       </c>
-      <c r="D10" t="n" s="0">
-        <v>2872.0</v>
-      </c>
-      <c r="E10" t="n" s="0">
-        <v>2875.0</v>
-      </c>
-      <c r="F10" t="s" s="0">
+      <c r="D10">
+        <v>2872</v>
+      </c>
+      <c r="E10">
+        <v>2875</v>
+      </c>
+      <c r="F10" t="s">
         <v>47</v>
       </c>
-      <c r="G10" t="s" s="0">
+      <c r="G10" t="s">
         <v>117</v>
       </c>
-      <c r="H10" s="0"/>
-      <c r="I10" s="0"/>
-      <c r="J10" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K10" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L10" t="s" s="0">
+      <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" t="s">
         <v>50</v>
       </c>
-      <c r="M10" t="s" s="0">
+      <c r="M10" t="s">
         <v>51</v>
       </c>
-      <c r="N10" t="s" s="0">
+      <c r="N10" t="s">
         <v>52</v>
       </c>
-      <c r="O10" t="s" s="0">
+      <c r="O10" t="s">
         <v>97</v>
       </c>
-      <c r="P10" t="s" s="0">
+      <c r="P10" t="s">
         <v>98</v>
       </c>
-      <c r="Q10" t="s" s="0">
+      <c r="Q10" t="s">
         <v>99</v>
       </c>
-      <c r="R10" t="s" s="0">
+      <c r="R10" t="s">
         <v>111</v>
       </c>
-      <c r="S10" s="0"/>
-      <c r="T10" t="s" s="0">
+      <c r="T10" t="s">
         <v>56</v>
       </c>
-      <c r="U10" t="s" s="0">
+      <c r="U10" t="s">
         <v>57</v>
       </c>
-      <c r="V10" t="s" s="0">
+      <c r="V10" t="s">
         <v>58</v>
       </c>
-      <c r="W10" t="s" s="0">
+      <c r="W10" t="s">
         <v>118</v>
       </c>
-      <c r="X10" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y10" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z10" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC10" t="s" s="0">
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="s">
         <v>60</v>
       </c>
-      <c r="AD10" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE10" t="n" s="1">
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
         <v>1012.73</v>
       </c>
-      <c r="AF10" t="n" s="1">
+      <c r="AF10" s="1">
         <v>9114.6</v>
       </c>
-      <c r="AG10" t="s" s="0">
+      <c r="AG10" t="s">
         <v>104</v>
       </c>
-      <c r="AH10" t="s" s="0">
+      <c r="AH10" t="s">
         <v>105</v>
       </c>
-      <c r="AI10" t="s" s="0">
+      <c r="AI10" t="s">
         <v>63</v>
       </c>
-      <c r="AJ10" t="s" s="0">
+      <c r="AJ10" t="s">
         <v>64</v>
       </c>
-      <c r="AK10" t="s" s="0">
+      <c r="AK10" t="s">
         <v>62</v>
       </c>
-      <c r="AL10" s="0"/>
-      <c r="AM10" s="0"/>
-      <c r="AN10" s="0"/>
-      <c r="AO10" s="0"/>
-      <c r="AP10" t="s" s="0">
+      <c r="AP10" t="s">
         <v>113</v>
       </c>
-      <c r="AQ10" t="s" s="0">
+      <c r="AQ10" t="s">
         <v>114</v>
       </c>
-      <c r="AR10" t="s" s="0">
+      <c r="AR10" t="s">
         <v>119</v>
       </c>
-      <c r="AS10" t="s" s="0">
+      <c r="AS10" t="s">
         <v>67</v>
       </c>
-      <c r="AT10" s="0"/>
-      <c r="AU10" t="s" s="0">
+      <c r="AU10" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="s" s="0">
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>44</v>
       </c>
-      <c r="B11" t="s" s="0">
+      <c r="B11" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s" s="0">
+      <c r="C11" t="s">
         <v>120</v>
       </c>
-      <c r="D11" t="n" s="0">
-        <v>2873.0</v>
-      </c>
-      <c r="E11" t="n" s="0">
-        <v>2877.0</v>
-      </c>
-      <c r="F11" t="s" s="0">
+      <c r="D11">
+        <v>2873</v>
+      </c>
+      <c r="E11">
+        <v>2877</v>
+      </c>
+      <c r="F11" t="s">
         <v>47</v>
       </c>
-      <c r="G11" t="s" s="0">
+      <c r="G11" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-      <c r="J11" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K11" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L11" t="s" s="0">
+      <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" t="s">
         <v>50</v>
       </c>
-      <c r="M11" t="s" s="0">
+      <c r="M11" t="s">
         <v>51</v>
       </c>
-      <c r="N11" t="s" s="0">
+      <c r="N11" t="s">
         <v>52</v>
       </c>
-      <c r="O11" t="s" s="0">
+      <c r="O11" t="s">
         <v>97</v>
       </c>
-      <c r="P11" t="s" s="0">
+      <c r="P11" t="s">
         <v>98</v>
       </c>
-      <c r="Q11" t="s" s="0">
+      <c r="Q11" t="s">
         <v>99</v>
       </c>
-      <c r="R11" t="s" s="0">
+      <c r="R11" t="s">
         <v>111</v>
       </c>
-      <c r="S11" s="0"/>
-      <c r="T11" t="s" s="0">
+      <c r="T11" t="s">
         <v>56</v>
       </c>
-      <c r="U11" t="s" s="0">
+      <c r="U11" t="s">
         <v>57</v>
       </c>
-      <c r="V11" t="s" s="0">
+      <c r="V11" t="s">
         <v>58</v>
       </c>
-      <c r="W11" t="s" s="0">
+      <c r="W11" t="s">
         <v>122</v>
       </c>
-      <c r="X11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC11" t="s" s="0">
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="s">
         <v>60</v>
       </c>
-      <c r="AD11" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE11" t="n" s="1">
-        <v>18.74</v>
-      </c>
-      <c r="AF11" t="n" s="1">
+      <c r="AD11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="1">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AF11" s="1">
         <v>168.66</v>
       </c>
-      <c r="AG11" t="s" s="0">
+      <c r="AG11" t="s">
         <v>104</v>
       </c>
-      <c r="AH11" t="s" s="0">
+      <c r="AH11" t="s">
         <v>105</v>
       </c>
-      <c r="AI11" t="s" s="0">
+      <c r="AI11" t="s">
         <v>63</v>
       </c>
-      <c r="AJ11" t="s" s="0">
+      <c r="AJ11" t="s">
         <v>64</v>
       </c>
-      <c r="AK11" t="s" s="0">
+      <c r="AK11" t="s">
         <v>62</v>
       </c>
-      <c r="AL11" s="0"/>
-      <c r="AM11" s="0"/>
-      <c r="AN11" s="0"/>
-      <c r="AO11" s="0"/>
-      <c r="AP11" t="s" s="0">
+      <c r="AP11" t="s">
         <v>113</v>
       </c>
-      <c r="AQ11" t="s" s="0">
+      <c r="AQ11" t="s">
         <v>114</v>
       </c>
-      <c r="AR11" t="s" s="0">
+      <c r="AR11" t="s">
         <v>123</v>
       </c>
-      <c r="AS11" t="s" s="0">
+      <c r="AS11" t="s">
         <v>67</v>
       </c>
-      <c r="AT11" s="0"/>
-      <c r="AU11" t="s" s="0">
+      <c r="AU11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="s" s="0">
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>44</v>
       </c>
-      <c r="B12" t="s" s="0">
+      <c r="B12" t="s">
         <v>45</v>
       </c>
-      <c r="C12" t="s" s="0">
+      <c r="C12" t="s">
         <v>124</v>
       </c>
-      <c r="D12" t="n" s="0">
-        <v>2874.0</v>
-      </c>
-      <c r="E12" t="n" s="0">
-        <v>2878.0</v>
-      </c>
-      <c r="F12" t="s" s="0">
+      <c r="D12">
+        <v>2874</v>
+      </c>
+      <c r="E12">
+        <v>2878</v>
+      </c>
+      <c r="F12" t="s">
         <v>47</v>
       </c>
-      <c r="G12" t="s" s="0">
+      <c r="G12" t="s">
         <v>125</v>
       </c>
-      <c r="H12" s="0"/>
-      <c r="I12" s="0"/>
-      <c r="J12" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K12" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L12" t="s" s="0">
+      <c r="J12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" t="s">
         <v>50</v>
       </c>
-      <c r="M12" t="s" s="0">
+      <c r="M12" t="s">
         <v>51</v>
       </c>
-      <c r="N12" t="s" s="0">
+      <c r="N12" t="s">
         <v>52</v>
       </c>
-      <c r="O12" t="s" s="0">
+      <c r="O12" t="s">
         <v>97</v>
       </c>
-      <c r="P12" t="s" s="0">
+      <c r="P12" t="s">
         <v>98</v>
       </c>
-      <c r="Q12" t="s" s="0">
+      <c r="Q12" t="s">
         <v>99</v>
       </c>
-      <c r="R12" t="s" s="0">
+      <c r="R12" t="s">
         <v>111</v>
       </c>
-      <c r="S12" s="0"/>
-      <c r="T12" t="s" s="0">
+      <c r="T12" t="s">
         <v>56</v>
       </c>
-      <c r="U12" t="s" s="0">
+      <c r="U12" t="s">
         <v>57</v>
       </c>
-      <c r="V12" t="s" s="0">
+      <c r="V12" t="s">
         <v>58</v>
       </c>
-      <c r="W12" t="s" s="0">
+      <c r="W12" t="s">
         <v>122</v>
       </c>
-      <c r="X12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC12" t="s" s="0">
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="s">
         <v>60</v>
       </c>
-      <c r="AD12" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE12" t="n" s="1">
-        <v>18.74</v>
-      </c>
-      <c r="AF12" t="n" s="1">
+      <c r="AD12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="1">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AF12" s="1">
         <v>168.66</v>
       </c>
-      <c r="AG12" t="s" s="0">
+      <c r="AG12" t="s">
         <v>104</v>
       </c>
-      <c r="AH12" t="s" s="0">
+      <c r="AH12" t="s">
         <v>105</v>
       </c>
-      <c r="AI12" t="s" s="0">
+      <c r="AI12" t="s">
         <v>63</v>
       </c>
-      <c r="AJ12" t="s" s="0">
+      <c r="AJ12" t="s">
         <v>64</v>
       </c>
-      <c r="AK12" t="s" s="0">
+      <c r="AK12" t="s">
         <v>62</v>
       </c>
-      <c r="AL12" s="0"/>
-      <c r="AM12" s="0"/>
-      <c r="AN12" s="0"/>
-      <c r="AO12" s="0"/>
-      <c r="AP12" t="s" s="0">
+      <c r="AP12" t="s">
         <v>113</v>
       </c>
-      <c r="AQ12" t="s" s="0">
+      <c r="AQ12" t="s">
         <v>114</v>
       </c>
-      <c r="AR12" t="s" s="0">
+      <c r="AR12" t="s">
         <v>126</v>
       </c>
-      <c r="AS12" t="s" s="0">
+      <c r="AS12" t="s">
         <v>67</v>
       </c>
-      <c r="AT12" s="0"/>
-      <c r="AU12" t="s" s="0">
+      <c r="AU12" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="s" s="0">
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" t="s" s="0">
+      <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" t="s" s="0">
+      <c r="C13" t="s">
         <v>127</v>
       </c>
-      <c r="D13" t="n" s="0">
-        <v>2875.0</v>
-      </c>
-      <c r="E13" t="n" s="0">
-        <v>2879.0</v>
-      </c>
-      <c r="F13" t="s" s="0">
+      <c r="D13">
+        <v>2875</v>
+      </c>
+      <c r="E13">
+        <v>2879</v>
+      </c>
+      <c r="F13" t="s">
         <v>47</v>
       </c>
-      <c r="G13" t="s" s="0">
+      <c r="G13" t="s">
         <v>128</v>
       </c>
-      <c r="H13" s="0"/>
-      <c r="I13" s="0"/>
-      <c r="J13" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K13" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L13" t="s" s="0">
+      <c r="J13" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" t="s">
         <v>50</v>
       </c>
-      <c r="M13" t="s" s="0">
+      <c r="M13" t="s">
         <v>51</v>
       </c>
-      <c r="N13" t="s" s="0">
+      <c r="N13" t="s">
         <v>52</v>
       </c>
-      <c r="O13" t="s" s="0">
+      <c r="O13" t="s">
         <v>97</v>
       </c>
-      <c r="P13" t="s" s="0">
+      <c r="P13" t="s">
         <v>98</v>
       </c>
-      <c r="Q13" t="s" s="0">
+      <c r="Q13" t="s">
         <v>99</v>
       </c>
-      <c r="R13" t="s" s="0">
+      <c r="R13" t="s">
         <v>111</v>
       </c>
-      <c r="S13" s="0"/>
-      <c r="T13" t="s" s="0">
+      <c r="T13" t="s">
         <v>56</v>
       </c>
-      <c r="U13" t="s" s="0">
+      <c r="U13" t="s">
         <v>57</v>
       </c>
-      <c r="V13" t="s" s="0">
+      <c r="V13" t="s">
         <v>58</v>
       </c>
-      <c r="W13" t="s" s="0">
+      <c r="W13" t="s">
         <v>122</v>
       </c>
-      <c r="X13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC13" t="s" s="0">
+      <c r="X13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="s">
         <v>60</v>
       </c>
-      <c r="AD13" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE13" t="n" s="1">
-        <v>18.74</v>
-      </c>
-      <c r="AF13" t="n" s="1">
+      <c r="AD13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AF13" s="1">
         <v>168.66</v>
       </c>
-      <c r="AG13" t="s" s="0">
+      <c r="AG13" t="s">
         <v>104</v>
       </c>
-      <c r="AH13" t="s" s="0">
+      <c r="AH13" t="s">
         <v>105</v>
       </c>
-      <c r="AI13" t="s" s="0">
+      <c r="AI13" t="s">
         <v>63</v>
       </c>
-      <c r="AJ13" t="s" s="0">
+      <c r="AJ13" t="s">
         <v>64</v>
       </c>
-      <c r="AK13" t="s" s="0">
+      <c r="AK13" t="s">
         <v>62</v>
       </c>
-      <c r="AL13" s="0"/>
-      <c r="AM13" s="0"/>
-      <c r="AN13" s="0"/>
-      <c r="AO13" s="0"/>
-      <c r="AP13" t="s" s="0">
+      <c r="AP13" t="s">
         <v>113</v>
       </c>
-      <c r="AQ13" t="s" s="0">
+      <c r="AQ13" t="s">
         <v>114</v>
       </c>
-      <c r="AR13" t="s" s="0">
+      <c r="AR13" t="s">
         <v>129</v>
       </c>
-      <c r="AS13" t="s" s="0">
+      <c r="AS13" t="s">
         <v>67</v>
       </c>
-      <c r="AT13" s="0"/>
-      <c r="AU13" t="s" s="0">
+      <c r="AU13" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s" s="0">
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s" s="0">
+      <c r="B14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s" s="0">
+      <c r="C14" t="s">
         <v>130</v>
       </c>
-      <c r="D14" t="n" s="0">
-        <v>2876.0</v>
-      </c>
-      <c r="E14" t="n" s="0">
-        <v>2880.0</v>
-      </c>
-      <c r="F14" t="s" s="0">
+      <c r="D14">
+        <v>2876</v>
+      </c>
+      <c r="E14">
+        <v>2880</v>
+      </c>
+      <c r="F14" t="s">
         <v>47</v>
       </c>
-      <c r="G14" t="s" s="0">
+      <c r="G14" t="s">
         <v>131</v>
       </c>
-      <c r="H14" s="0"/>
-      <c r="I14" s="0"/>
-      <c r="J14" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K14" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L14" t="s" s="0">
+      <c r="J14" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" t="s">
         <v>50</v>
       </c>
-      <c r="M14" t="s" s="0">
+      <c r="M14" t="s">
         <v>51</v>
       </c>
-      <c r="N14" t="s" s="0">
+      <c r="N14" t="s">
         <v>52</v>
       </c>
-      <c r="O14" t="s" s="0">
+      <c r="O14" t="s">
         <v>97</v>
       </c>
-      <c r="P14" t="s" s="0">
+      <c r="P14" t="s">
         <v>98</v>
       </c>
-      <c r="Q14" t="s" s="0">
+      <c r="Q14" t="s">
         <v>99</v>
       </c>
-      <c r="R14" t="s" s="0">
+      <c r="R14" t="s">
         <v>111</v>
       </c>
-      <c r="S14" s="0"/>
-      <c r="T14" t="s" s="0">
+      <c r="T14" t="s">
         <v>56</v>
       </c>
-      <c r="U14" t="s" s="0">
+      <c r="U14" t="s">
         <v>57</v>
       </c>
-      <c r="V14" t="s" s="0">
+      <c r="V14" t="s">
         <v>58</v>
       </c>
-      <c r="W14" t="s" s="0">
+      <c r="W14" t="s">
         <v>132</v>
       </c>
-      <c r="X14" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y14" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z14" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA14" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB14" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC14" t="s" s="0">
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="s">
         <v>60</v>
       </c>
-      <c r="AD14" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE14" t="n" s="1">
+      <c r="AD14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="1">
         <v>1.08</v>
       </c>
-      <c r="AF14" t="n" s="1">
-        <v>9.7</v>
-      </c>
-      <c r="AG14" t="s" s="0">
+      <c r="AF14" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="AG14" t="s">
         <v>104</v>
       </c>
-      <c r="AH14" t="s" s="0">
+      <c r="AH14" t="s">
         <v>105</v>
       </c>
-      <c r="AI14" t="s" s="0">
+      <c r="AI14" t="s">
         <v>63</v>
       </c>
-      <c r="AJ14" t="s" s="0">
+      <c r="AJ14" t="s">
         <v>64</v>
       </c>
-      <c r="AK14" t="s" s="0">
+      <c r="AK14" t="s">
         <v>62</v>
       </c>
-      <c r="AL14" s="0"/>
-      <c r="AM14" s="0"/>
-      <c r="AN14" s="0"/>
-      <c r="AO14" s="0"/>
-      <c r="AP14" t="s" s="0">
+      <c r="AP14" t="s">
         <v>113</v>
       </c>
-      <c r="AQ14" t="s" s="0">
+      <c r="AQ14" t="s">
         <v>114</v>
       </c>
-      <c r="AR14" t="s" s="0">
+      <c r="AR14" t="s">
         <v>133</v>
       </c>
-      <c r="AS14" t="s" s="0">
+      <c r="AS14" t="s">
         <v>67</v>
       </c>
-      <c r="AT14" s="0"/>
-      <c r="AU14" t="s" s="0">
+      <c r="AU14" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s" s="0">
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s" s="0">
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s" s="0">
+      <c r="C15" t="s">
         <v>134</v>
       </c>
-      <c r="D15" t="n" s="0">
-        <v>2877.0</v>
-      </c>
-      <c r="E15" t="n" s="0">
-        <v>2881.0</v>
-      </c>
-      <c r="F15" t="s" s="0">
+      <c r="D15">
+        <v>2877</v>
+      </c>
+      <c r="E15">
+        <v>2881</v>
+      </c>
+      <c r="F15" t="s">
         <v>47</v>
       </c>
-      <c r="G15" t="s" s="0">
+      <c r="G15" t="s">
         <v>135</v>
       </c>
-      <c r="H15" s="0"/>
-      <c r="I15" s="0"/>
-      <c r="J15" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K15" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L15" t="s" s="0">
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" t="s">
         <v>50</v>
       </c>
-      <c r="M15" t="s" s="0">
+      <c r="M15" t="s">
         <v>51</v>
       </c>
-      <c r="N15" t="s" s="0">
+      <c r="N15" t="s">
         <v>52</v>
       </c>
-      <c r="O15" t="s" s="0">
+      <c r="O15" t="s">
         <v>97</v>
       </c>
-      <c r="P15" t="s" s="0">
+      <c r="P15" t="s">
         <v>98</v>
       </c>
-      <c r="Q15" t="s" s="0">
+      <c r="Q15" t="s">
         <v>99</v>
       </c>
-      <c r="R15" t="s" s="0">
+      <c r="R15" t="s">
         <v>111</v>
       </c>
-      <c r="S15" s="0"/>
-      <c r="T15" t="s" s="0">
+      <c r="T15" t="s">
         <v>56</v>
       </c>
-      <c r="U15" t="s" s="0">
+      <c r="U15" t="s">
         <v>57</v>
       </c>
-      <c r="V15" t="s" s="0">
+      <c r="V15" t="s">
         <v>58</v>
       </c>
-      <c r="W15" t="s" s="0">
+      <c r="W15" t="s">
         <v>136</v>
       </c>
-      <c r="X15" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Y15" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z15" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA15" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB15" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC15" t="s" s="0">
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="s">
         <v>60</v>
       </c>
-      <c r="AD15" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE15" t="n" s="1">
-        <v>18.74</v>
-      </c>
-      <c r="AF15" t="n" s="1">
+      <c r="AD15" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AF15" s="1">
         <v>168.66</v>
       </c>
-      <c r="AG15" t="s" s="0">
+      <c r="AG15" t="s">
         <v>104</v>
       </c>
-      <c r="AH15" t="s" s="0">
+      <c r="AH15" t="s">
         <v>105</v>
       </c>
-      <c r="AI15" t="s" s="0">
+      <c r="AI15" t="s">
         <v>63</v>
       </c>
-      <c r="AJ15" t="s" s="0">
+      <c r="AJ15" t="s">
         <v>64</v>
       </c>
-      <c r="AK15" t="s" s="0">
+      <c r="AK15" t="s">
         <v>62</v>
       </c>
-      <c r="AL15" s="0"/>
-      <c r="AM15" s="0"/>
-      <c r="AN15" s="0"/>
-      <c r="AO15" s="0"/>
-      <c r="AP15" t="s" s="0">
+      <c r="AP15" t="s">
         <v>113</v>
       </c>
-      <c r="AQ15" t="s" s="0">
+      <c r="AQ15" t="s">
         <v>114</v>
       </c>
-      <c r="AR15" t="s" s="0">
+      <c r="AR15" t="s">
         <v>137</v>
       </c>
-      <c r="AS15" t="s" s="0">
+      <c r="AS15" t="s">
         <v>67</v>
       </c>
-      <c r="AT15" s="0"/>
-      <c r="AU15" t="s" s="0">
+      <c r="AU15" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="0">
+    <row r="16" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s" s="0">
+      <c r="B16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s" s="0">
+      <c r="C16" t="s">
         <v>138</v>
       </c>
-      <c r="D16" t="n" s="0">
-        <v>2878.0</v>
-      </c>
-      <c r="E16" t="n" s="0">
-        <v>2882.0</v>
-      </c>
-      <c r="F16" t="s" s="0">
+      <c r="D16">
+        <v>2878</v>
+      </c>
+      <c r="E16">
+        <v>2882</v>
+      </c>
+      <c r="F16" t="s">
         <v>47</v>
       </c>
-      <c r="G16" t="s" s="0">
+      <c r="G16" t="s">
         <v>139</v>
       </c>
-      <c r="H16" s="0"/>
-      <c r="I16" s="0"/>
-      <c r="J16" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K16" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L16" t="s" s="0">
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" t="s">
         <v>50</v>
       </c>
-      <c r="M16" t="s" s="0">
+      <c r="M16" t="s">
         <v>51</v>
       </c>
-      <c r="N16" t="s" s="0">
+      <c r="N16" t="s">
         <v>52</v>
       </c>
-      <c r="O16" t="s" s="0">
+      <c r="O16" t="s">
         <v>140</v>
       </c>
-      <c r="P16" s="0"/>
-      <c r="Q16" t="s" s="0">
+      <c r="Q16" t="s">
         <v>141</v>
       </c>
-      <c r="R16" t="s" s="0">
+      <c r="R16" t="s">
         <v>142</v>
       </c>
-      <c r="S16" s="0"/>
-      <c r="T16" t="s" s="0">
+      <c r="T16" t="s">
         <v>56</v>
       </c>
-      <c r="U16" t="s" s="0">
+      <c r="U16" t="s">
         <v>57</v>
       </c>
-      <c r="V16" t="s" s="0">
+      <c r="V16" t="s">
         <v>58</v>
       </c>
-      <c r="W16" t="s" s="0">
+      <c r="W16" t="s">
         <v>143</v>
       </c>
-      <c r="X16" t="n" s="1">
+      <c r="X16" s="1">
         <v>48340.18</v>
       </c>
-      <c r="Y16" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z16" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA16" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB16" t="n" s="1">
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="1">
         <v>48340.18</v>
       </c>
-      <c r="AC16" t="s" s="0">
+      <c r="AC16" t="s">
         <v>60</v>
       </c>
-      <c r="AD16" t="n" s="1">
+      <c r="AD16" s="1">
         <v>966.8</v>
       </c>
-      <c r="AE16" t="n" s="1">
+      <c r="AE16" s="1">
         <v>47.37</v>
       </c>
-      <c r="AF16" t="n" s="1">
+      <c r="AF16" s="1">
         <v>426.36</v>
       </c>
-      <c r="AG16" t="s" s="0">
+      <c r="AG16" t="s">
         <v>61</v>
       </c>
-      <c r="AH16" t="s" s="0">
+      <c r="AH16" t="s">
         <v>62</v>
       </c>
-      <c r="AI16" t="s" s="0">
+      <c r="AI16" t="s">
         <v>63</v>
       </c>
-      <c r="AJ16" t="s" s="0">
+      <c r="AJ16" t="s">
         <v>64</v>
       </c>
-      <c r="AK16" t="s" s="0">
+      <c r="AK16" t="s">
         <v>62</v>
       </c>
-      <c r="AL16" s="0"/>
-      <c r="AM16" s="0"/>
-      <c r="AN16" s="0"/>
-      <c r="AO16" s="0"/>
-      <c r="AP16" t="s" s="0">
+      <c r="AP16" t="s">
         <v>65</v>
       </c>
-      <c r="AQ16" s="0"/>
-      <c r="AR16" t="s" s="0">
+      <c r="AR16" t="s">
         <v>66</v>
       </c>
-      <c r="AS16" t="s" s="0">
+      <c r="AS16" t="s">
         <v>67</v>
       </c>
-      <c r="AT16" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU16" t="s" s="0">
+      <c r="AT16">
+        <v>100586516</v>
+      </c>
+      <c r="AU16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="s" s="0">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" t="s" s="0">
+      <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="C17" t="s" s="0">
+      <c r="C17" t="s">
         <v>144</v>
       </c>
-      <c r="D17" t="n" s="0">
-        <v>2879.0</v>
-      </c>
-      <c r="E17" s="0"/>
-      <c r="F17" t="s" s="0">
+      <c r="D17">
+        <v>2879</v>
+      </c>
+      <c r="F17" t="s">
         <v>47</v>
       </c>
-      <c r="G17" t="s" s="0">
+      <c r="G17" t="s">
         <v>145</v>
       </c>
-      <c r="H17" s="0"/>
-      <c r="I17" s="0"/>
-      <c r="J17" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K17" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L17" t="s" s="0">
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" t="s">
         <v>50</v>
       </c>
-      <c r="M17" t="s" s="0">
+      <c r="M17" t="s">
         <v>51</v>
       </c>
-      <c r="N17" t="s" s="0">
+      <c r="N17" t="s">
         <v>52</v>
       </c>
-      <c r="O17" t="s" s="0">
+      <c r="O17" t="s">
         <v>97</v>
       </c>
-      <c r="P17" t="s" s="0">
+      <c r="P17" t="s">
         <v>98</v>
       </c>
-      <c r="Q17" t="s" s="0">
+      <c r="Q17" t="s">
         <v>99</v>
       </c>
-      <c r="R17" t="s" s="0">
+      <c r="R17" t="s">
         <v>100</v>
       </c>
-      <c r="S17" s="0"/>
-      <c r="T17" t="s" s="0">
+      <c r="T17" t="s">
         <v>56</v>
       </c>
-      <c r="U17" t="s" s="0">
+      <c r="U17" t="s">
         <v>57</v>
       </c>
-      <c r="V17" t="s" s="0">
+      <c r="V17" t="s">
         <v>58</v>
       </c>
-      <c r="W17" t="s" s="0">
+      <c r="W17" t="s">
         <v>103</v>
       </c>
-      <c r="X17" t="n" s="1">
+      <c r="X17" s="1">
         <v>19122.09</v>
       </c>
-      <c r="Y17" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z17" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA17" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB17" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC17" t="s" s="0">
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="s">
         <v>60</v>
       </c>
-      <c r="AD17" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE17" t="n" s="1">
-        <v>18.74</v>
-      </c>
-      <c r="AF17" t="n" s="1">
+      <c r="AD17" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="AF17" s="1">
         <v>168.66</v>
       </c>
-      <c r="AG17" t="s" s="0">
+      <c r="AG17" t="s">
         <v>104</v>
       </c>
-      <c r="AH17" t="s" s="0">
+      <c r="AH17" t="s">
         <v>105</v>
       </c>
-      <c r="AI17" t="s" s="0">
+      <c r="AI17" t="s">
         <v>63</v>
       </c>
-      <c r="AJ17" t="s" s="0">
+      <c r="AJ17" t="s">
         <v>64</v>
       </c>
-      <c r="AK17" t="s" s="0">
+      <c r="AK17" t="s">
         <v>62</v>
       </c>
-      <c r="AL17" t="s" s="0">
+      <c r="AL17" t="s">
         <v>106</v>
       </c>
-      <c r="AM17" t="n" s="0">
-        <v>30101.0</v>
-      </c>
-      <c r="AN17" t="s" s="0">
+      <c r="AM17">
+        <v>30101</v>
+      </c>
+      <c r="AN17" t="s">
         <v>107</v>
       </c>
-      <c r="AO17" t="s" s="0">
+      <c r="AO17" t="s">
         <v>108</v>
       </c>
-      <c r="AP17" t="s" s="0">
+      <c r="AP17" t="s">
         <v>65</v>
       </c>
-      <c r="AQ17" s="0"/>
-      <c r="AR17" t="s" s="0">
+      <c r="AR17" t="s">
         <v>66</v>
       </c>
-      <c r="AS17" t="s" s="0">
+      <c r="AS17" t="s">
         <v>67</v>
       </c>
-      <c r="AT17" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU17" t="s" s="0">
+      <c r="AT17">
+        <v>100586516</v>
+      </c>
+      <c r="AU17" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="s" s="0">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>44</v>
       </c>
-      <c r="B18" t="s" s="0">
+      <c r="B18" t="s">
         <v>45</v>
       </c>
-      <c r="C18" t="s" s="0">
+      <c r="C18" t="s">
         <v>146</v>
       </c>
-      <c r="D18" t="n" s="0">
-        <v>2880.0</v>
-      </c>
-      <c r="E18" s="0"/>
-      <c r="F18" t="s" s="0">
+      <c r="D18">
+        <v>2880</v>
+      </c>
+      <c r="F18" t="s">
         <v>47</v>
       </c>
-      <c r="G18" t="s" s="0">
+      <c r="G18" t="s">
         <v>147</v>
       </c>
-      <c r="H18" s="0"/>
-      <c r="I18" s="0"/>
-      <c r="J18" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="K18" t="s" s="0">
-        <v>49</v>
-      </c>
-      <c r="L18" t="s" s="0">
+      <c r="J18" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" t="s">
         <v>50</v>
       </c>
-      <c r="M18" t="s" s="0">
+      <c r="M18" t="s">
         <v>51</v>
       </c>
-      <c r="N18" t="s" s="0">
+      <c r="N18" t="s">
         <v>52</v>
       </c>
-      <c r="O18" t="s" s="0">
+      <c r="O18" t="s">
         <v>97</v>
       </c>
-      <c r="P18" t="s" s="0">
+      <c r="P18" t="s">
         <v>98</v>
       </c>
-      <c r="Q18" t="s" s="0">
+      <c r="Q18" t="s">
         <v>99</v>
       </c>
-      <c r="R18" t="s" s="0">
+      <c r="R18" t="s">
         <v>100</v>
       </c>
-      <c r="S18" s="0"/>
-      <c r="T18" t="s" s="0">
+      <c r="T18" t="s">
         <v>56</v>
       </c>
-      <c r="U18" t="s" s="0">
+      <c r="U18" t="s">
         <v>57</v>
       </c>
-      <c r="V18" t="s" s="0">
+      <c r="V18" t="s">
         <v>58</v>
       </c>
-      <c r="W18" t="s" s="0">
+      <c r="W18" t="s">
         <v>103</v>
       </c>
-      <c r="X18" t="n" s="1">
+      <c r="X18" s="1">
         <v>2697.3</v>
       </c>
-      <c r="Y18" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Z18" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AA18" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AB18" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AC18" t="s" s="0">
+      <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="s">
         <v>60</v>
       </c>
-      <c r="AD18" t="n" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="AE18" t="n" s="1">
+      <c r="AD18" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="1">
         <v>2.64</v>
       </c>
-      <c r="AF18" t="n" s="1">
+      <c r="AF18" s="1">
         <v>23.79</v>
       </c>
-      <c r="AG18" t="s" s="0">
+      <c r="AG18" t="s">
         <v>104</v>
       </c>
-      <c r="AH18" t="s" s="0">
+      <c r="AH18" t="s">
         <v>105</v>
       </c>
-      <c r="AI18" t="s" s="0">
+      <c r="AI18" t="s">
         <v>63</v>
       </c>
-      <c r="AJ18" t="s" s="0">
+      <c r="AJ18" t="s">
         <v>64</v>
       </c>
-      <c r="AK18" t="s" s="0">
+      <c r="AK18" t="s">
         <v>62</v>
       </c>
-      <c r="AL18" t="s" s="0">
+      <c r="AL18" t="s">
         <v>106</v>
       </c>
-      <c r="AM18" t="n" s="0">
-        <v>30101.0</v>
-      </c>
-      <c r="AN18" t="s" s="0">
+      <c r="AM18">
+        <v>30101</v>
+      </c>
+      <c r="AN18" t="s">
         <v>107</v>
       </c>
-      <c r="AO18" t="s" s="0">
+      <c r="AO18" t="s">
         <v>108</v>
       </c>
-      <c r="AP18" t="s" s="0">
+      <c r="AP18" t="s">
         <v>65</v>
       </c>
-      <c r="AQ18" s="0"/>
-      <c r="AR18" t="s" s="0">
+      <c r="AR18" t="s">
         <v>66</v>
       </c>
-      <c r="AS18" t="s" s="0">
+      <c r="AS18" t="s">
         <v>67</v>
       </c>
-      <c r="AT18" t="n" s="0">
-        <v>1.00586516E8</v>
-      </c>
-      <c r="AU18" t="s" s="0">
+      <c r="AT18">
+        <v>100586516</v>
+      </c>
+      <c r="AU18" t="s">
         <v>146</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>